--- a/Payments_Refunds/outputs/refund_recon_20251216_141501/refund_reconciliation_detailed.xlsx
+++ b/Payments_Refunds/outputs/refund_recon_20251216_141501/refund_reconciliation_detailed.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Payments Reconciliation\Payments_Refunds\outputs\refund_recon_20251216_141501\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Payments Reconciliation\Payments_Refunds\outputs\refund_recon_20251216_141501\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -3715,7 +3715,13 @@
     <col min="4" max="4" width="17.5703125" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" customWidth="1"/>
     <col min="6" max="6" width="27.140625" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="22.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="17.140625" customWidth="1"/>
     <col min="14" max="14" width="29.7109375" customWidth="1"/>
     <col min="15" max="15" width="41.28515625" customWidth="1"/>
   </cols>
